--- a/SoRoSim Robots/my_robot(1.75)(3tendon)/10-09-2025 V2/Validation(1.75)(3tendon).xlsx
+++ b/SoRoSim Robots/my_robot(1.75)(3tendon)/10-09-2025 V2/Validation(1.75)(3tendon).xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(1.75)(3tendon)/10-09-2025 V2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2010" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{021D004E-17D6-484C-8BBB-815F477FD575}"/>
+  <xr:revisionPtr revIDLastSave="2051" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8CF75C3-4B8C-4B9A-9E67-CE79D3F29DDA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (single)" sheetId="8" r:id="rId1"/>
     <sheet name="Distal Validation (single)" sheetId="9" r:id="rId2"/>
-    <sheet name="Distal Vali (single, w noise)" sheetId="12" r:id="rId3"/>
-    <sheet name="Conversion" sheetId="4" r:id="rId4"/>
+    <sheet name="Distal Vali (0.2 prop noise)" sheetId="12" r:id="rId3"/>
+    <sheet name="Distal Vali (add noise)" sheetId="14" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId5"/>
+    <sheet name="Conversion" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="33">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -373,7 +375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -441,6 +443,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -462,6 +465,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -782,12 +789,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22B4A24-01F9-43FA-AE7F-5A1710EEAA53}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>13</v>
       </c>
@@ -822,7 +829,7 @@
       <c r="X1" s="19"/>
       <c r="Y1" s="20"/>
     </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -899,7 +906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>0.3</v>
       </c>
@@ -982,7 +989,7 @@
         <v>2.5427382816280791E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>0.4</v>
       </c>
@@ -1065,7 +1072,7 @@
         <v>6.6780997899981265E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>0.6</v>
       </c>
@@ -1148,7 +1155,7 @@
         <v>4.2798445315653799E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>0.4</v>
       </c>
@@ -1231,7 +1238,7 @@
         <v>1.263124733892923E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>0.8</v>
       </c>
@@ -1314,7 +1321,7 @@
         <v>5.845003931113979E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>0.7</v>
       </c>
@@ -1397,7 +1404,7 @@
         <v>4.3812257797486542E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>0.7</v>
       </c>
@@ -1480,7 +1487,7 @@
         <v>2.7298976201357572E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>0.7</v>
       </c>
@@ -1563,7 +1570,7 @@
         <v>2.9630353024580891E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>0.6</v>
       </c>
@@ -1646,7 +1653,7 @@
         <v>1.0942110609346495E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>0.8</v>
       </c>
@@ -1729,7 +1736,7 @@
         <v>0.11182919344780234</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>0.4</v>
       </c>
@@ -1812,7 +1819,7 @@
         <v>4.1290518015808908E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>0.4</v>
       </c>
@@ -1895,7 +1902,7 @@
         <v>2.5035708808014728E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>0.7</v>
       </c>
@@ -1978,7 +1985,7 @@
         <v>8.9354579936747336E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>0.4</v>
       </c>
@@ -2061,7 +2068,7 @@
         <v>2.7505587272357607E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <v>0.3</v>
       </c>
@@ -2159,29 +2166,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D6F75F-00D5-499A-8B94-C01DFDD9DEC2}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
@@ -2218,7 +2225,7 @@
       <c r="X1" s="21"/>
       <c r="Y1" s="21"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2298,7 +2305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <f>'Proximal Validation (single)'!A3</f>
         <v>0.3</v>
@@ -2399,7 +2406,7 @@
         <v>9.6009574982339016E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <f>'Proximal Validation (single)'!A4</f>
         <v>0.4</v>
@@ -2492,7 +2499,7 @@
         <v>5.5009434393328407</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <f>'Proximal Validation (single)'!A5</f>
         <v>0.6</v>
@@ -2577,7 +2584,7 @@
         <v>0.15499006469466325</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f>'Proximal Validation (single)'!A6</f>
         <v>0.4</v>
@@ -2662,7 +2669,7 @@
         <v>6.1693349312047507E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f>'Proximal Validation (single)'!A7</f>
         <v>0.8</v>
@@ -2747,7 +2754,7 @@
         <v>3.8559705414278111E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f>'Proximal Validation (single)'!A8</f>
         <v>0.7</v>
@@ -2832,7 +2839,7 @@
         <v>5.5025412034901411E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f>'Proximal Validation (single)'!A9</f>
         <v>0.7</v>
@@ -2917,7 +2924,7 @@
         <v>7.580897839119527E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f>'Proximal Validation (single)'!A10</f>
         <v>0.7</v>
@@ -3002,7 +3009,7 @@
         <v>7.6347716102113772E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f>'Proximal Validation (single)'!A11</f>
         <v>0.6</v>
@@ -3087,7 +3094,7 @@
         <v>0.11473659818591442</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f>'Proximal Validation (single)'!A12</f>
         <v>0.8</v>
@@ -3172,7 +3179,7 @@
         <v>0.2397951010237892</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f>'Proximal Validation (single)'!A13</f>
         <v>0.4</v>
@@ -3257,7 +3264,7 @@
         <v>0.14928535802882015</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f>'Proximal Validation (single)'!A14</f>
         <v>0.4</v>
@@ -3342,7 +3349,7 @@
         <v>3.3489331226959074E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f>'Proximal Validation (single)'!A15</f>
         <v>0.7</v>
@@ -3427,7 +3434,7 @@
         <v>8.0021837185958899E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f>'Proximal Validation (single)'!A16</f>
         <v>0.4</v>
@@ -3512,7 +3519,7 @@
         <v>5.9000710376845067E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <f>'Proximal Validation (single)'!A17</f>
         <v>0.3</v>
@@ -3613,29 +3620,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C7F774-9DF3-4E6E-BB0A-FE0B8E71539C}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
@@ -3672,7 +3679,7 @@
       <c r="X1" s="21"/>
       <c r="Y1" s="21"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3752,7 +3759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <f>'Proximal Validation (single)'!A3</f>
         <v>0.3</v>
@@ -3805,45 +3812,55 @@
         <f>'Proximal Validation (single)'!M3</f>
         <v>0.198836579918861</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="10"/>
+      <c r="N3" s="9">
+        <v>0.25546830737307386</v>
+      </c>
+      <c r="O3" s="9">
+        <v>7.8868414103961892E-2</v>
+      </c>
+      <c r="P3" s="9">
+        <v>1.6181648005651359</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0.88264411592348146</v>
+      </c>
+      <c r="R3" s="10">
+        <v>7.8113581943027076E-7</v>
+      </c>
       <c r="S3" s="8">
         <f>ABS(N3-A3)</f>
-        <v>0.3</v>
+        <v>4.4531692626926134E-2</v>
       </c>
       <c r="T3" s="8">
         <f t="shared" ref="T3:V17" si="0">ABS(O3-B3)</f>
-        <v>0.08</v>
+        <v>1.1315858960381092E-3</v>
       </c>
       <c r="U3" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>4.7164800565135945E-2</v>
       </c>
       <c r="V3" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
+        <v>9.7644115923481434E-2</v>
       </c>
       <c r="W3" s="9">
         <f>AVERAGE(S3:S17)</f>
-        <v>0.54666666666666675</v>
+        <v>5.2476209197665491E-2</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" ref="X3:Z3" si="1">AVERAGE(T3:T17)</f>
-        <v>0.13066666666666668</v>
+        <v>3.5238875729212249E-2</v>
       </c>
       <c r="Y3" s="9">
         <f>AVERAGE(U3:U17)</f>
-        <v>2.6877999999999997</v>
+        <v>1.9772421376657513E-2</v>
       </c>
       <c r="Z3" s="9">
         <f t="shared" si="1"/>
-        <v>1.2042000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>8.1219273691134311E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <f>'Proximal Validation (single)'!A4</f>
         <v>0.4</v>
@@ -3896,37 +3913,47 @@
         <f>'Proximal Validation (single)'!M4</f>
         <v>0.25498384237289401</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="10"/>
+      <c r="N4" s="9">
+        <v>0.32609333192246198</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0.14396765138446288</v>
+      </c>
+      <c r="P4" s="9">
+        <v>1.5671820177231277</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0.81117679681815691</v>
+      </c>
+      <c r="R4" s="10">
+        <v>8.7486293246918095E-8</v>
+      </c>
       <c r="S4" s="8">
         <f t="shared" ref="S4:S17" si="2">ABS(N4-A4)</f>
-        <v>0.4</v>
+        <v>7.390666807753804E-2</v>
       </c>
       <c r="T4" s="8">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>3.9676513844628669E-3</v>
       </c>
       <c r="U4" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>3.8179822768722449E-3</v>
       </c>
       <c r="V4" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
+        <v>2.6176796818156878E-2</v>
       </c>
       <c r="Y4">
         <f>DEGREES(Y3)</f>
-        <v>153.99959617526267</v>
+        <v>1.1328762956367244</v>
       </c>
       <c r="Z4">
         <f>DEGREES(Z3)</f>
-        <v>68.995577689653743</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.6535215976199193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <f>'Proximal Validation (single)'!A5</f>
         <v>0.6</v>
@@ -3979,29 +4006,39 @@
         <f>'Proximal Validation (single)'!M5</f>
         <v>0.50102174282073997</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="10"/>
+      <c r="N5" s="9">
+        <v>0.57078976457573982</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0.16313417724829826</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1.6797349194716533</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0.79738512393807259</v>
+      </c>
+      <c r="R5" s="10">
+        <v>9.2837655331362166E-6</v>
+      </c>
       <c r="S5" s="8">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>2.9210235424260156E-2</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>3.1341772482982588E-3</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>0.10873491947165337</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.2385123938072562E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f>'Proximal Validation (single)'!A6</f>
         <v>0.4</v>
@@ -4054,29 +4091,39 @@
         <f>'Proximal Validation (single)'!M6</f>
         <v>0.38675421476364102</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="10"/>
+      <c r="N6" s="9">
+        <v>0.40034285871753178</v>
+      </c>
+      <c r="O6" s="9">
+        <v>6.3789557915673353E-2</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1.586671848800391</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1.5139212151584278</v>
+      </c>
+      <c r="R6" s="10">
+        <v>1.2081842601851074E-7</v>
+      </c>
       <c r="S6" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>3.4285871753175767E-4</v>
       </c>
       <c r="T6" s="8">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>3.7895579156733555E-3</v>
       </c>
       <c r="U6" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>1.5671848800391075E-2</v>
       </c>
       <c r="V6" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5.7078784841572139E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f>'Proximal Validation (single)'!A7</f>
         <v>0.8</v>
@@ -4129,29 +4176,39 @@
         <f>'Proximal Validation (single)'!M7</f>
         <v>0.85134243965148904</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="10"/>
+      <c r="N7" s="9">
+        <v>0.88572261201942548</v>
+      </c>
+      <c r="O7" s="9">
+        <v>8.3569789489519986E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <v>1.5739509948092629</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.5112353760358364</v>
+      </c>
+      <c r="R7" s="10">
+        <v>1.3970315553094521E-7</v>
+      </c>
       <c r="S7" s="8">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>8.5722612019425437E-2</v>
       </c>
       <c r="T7" s="8">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>3.5697894895199839E-3</v>
       </c>
       <c r="U7" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>2.9509948092629745E-3</v>
       </c>
       <c r="V7" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5.9764623964163599E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f>'Proximal Validation (single)'!A8</f>
         <v>0.7</v>
@@ -4204,29 +4261,39 @@
         <f>'Proximal Validation (single)'!M8</f>
         <v>0.56537818908691395</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="10"/>
+      <c r="N8" s="9">
+        <v>0.62779646510893539</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0.17006510238176295</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1.616076604121921</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>1.4155644303124766</v>
+      </c>
+      <c r="R8" s="10">
+        <v>6.9471785774708248E-6</v>
+      </c>
       <c r="S8" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>7.2203534891064569E-2</v>
       </c>
       <c r="T8" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>1.0065102381762947E-2</v>
       </c>
       <c r="U8" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>4.5076604121921049E-2</v>
       </c>
       <c r="V8" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.15543556968752337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f>'Proximal Validation (single)'!A9</f>
         <v>0.7</v>
@@ -4279,29 +4346,39 @@
         <f>'Proximal Validation (single)'!M9</f>
         <v>0.55889892578125</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="10"/>
+      <c r="N9" s="9">
+        <v>0.66248085357426356</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1.5733653769085645</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>1.394077841401874</v>
+      </c>
+      <c r="R9" s="10">
+        <v>2.1300105319310258E-4</v>
+      </c>
       <c r="S9" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>3.7519146425736394E-2</v>
       </c>
       <c r="T9" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U9" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>2.3653769085645315E-3</v>
       </c>
       <c r="V9" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.17692215859812599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f>'Proximal Validation (single)'!A10</f>
         <v>0.7</v>
@@ -4354,29 +4431,39 @@
         <f>'Proximal Validation (single)'!M10</f>
         <v>-0.28826642036437999</v>
       </c>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="10"/>
+      <c r="N10" s="9">
+        <v>0.78011865781311185</v>
+      </c>
+      <c r="O10" s="9">
+        <v>1.3891682172543376E-2</v>
+      </c>
+      <c r="P10" s="9">
+        <v>3.6489646853526301</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0.90957978820062912</v>
+      </c>
+      <c r="R10" s="10">
+        <v>1.9591918862133664E-4</v>
+      </c>
       <c r="S10" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>8.0118657813111893E-2</v>
       </c>
       <c r="T10" s="8">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>4.610831782745662E-2</v>
       </c>
       <c r="U10" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.6035314647369958E-2</v>
       </c>
       <c r="V10" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.12457978820062909</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f>'Proximal Validation (single)'!A11</f>
         <v>0.6</v>
@@ -4429,29 +4516,39 @@
         <f>'Proximal Validation (single)'!M11</f>
         <v>-0.223745286464691</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="10"/>
+      <c r="N11" s="9">
+        <v>0.59833706306402712</v>
+      </c>
+      <c r="O11" s="9">
+        <v>4.0348393230003624E-2</v>
+      </c>
+      <c r="P11" s="9">
+        <v>3.6436113556561596</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0.92307624314530279</v>
+      </c>
+      <c r="R11" s="10">
+        <v>1.8216529345171185E-4</v>
+      </c>
       <c r="S11" s="8">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>1.6629369359728585E-3</v>
       </c>
       <c r="T11" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>5.9651606769996382E-2</v>
       </c>
       <c r="U11" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>2.1388644343840468E-2</v>
       </c>
       <c r="V11" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.13807624314530276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f>'Proximal Validation (single)'!A12</f>
         <v>0.8</v>
@@ -4504,29 +4601,39 @@
         <f>'Proximal Validation (single)'!M12</f>
         <v>-0.25870200991630599</v>
       </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="10"/>
+      <c r="N12" s="9">
+        <v>0.67321896357163991</v>
+      </c>
+      <c r="O12" s="9">
+        <v>8.8417225267400562E-2</v>
+      </c>
+      <c r="P12" s="9">
+        <v>3.6487541484407475</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0.92163844742106038</v>
+      </c>
+      <c r="R12" s="10">
+        <v>5.0169105666314072E-4</v>
+      </c>
       <c r="S12" s="8">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.12678103642836014</v>
       </c>
       <c r="T12" s="8">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>9.1582774732599431E-2</v>
       </c>
       <c r="U12" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.6245851559252511E-2</v>
       </c>
       <c r="V12" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.13663844742106035</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f>'Proximal Validation (single)'!A13</f>
         <v>0.4</v>
@@ -4579,29 +4686,39 @@
         <f>'Proximal Validation (single)'!M13</f>
         <v>-0.122712507843971</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="10"/>
+      <c r="N13" s="9">
+        <v>0.3291159927351901</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.11345412731669735</v>
+      </c>
+      <c r="P13" s="9">
+        <v>3.6698591378096403</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0.87160758209516287</v>
+      </c>
+      <c r="R13" s="10">
+        <v>1.3345208213857653E-4</v>
+      </c>
       <c r="S13" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>7.0884007264809923E-2</v>
       </c>
       <c r="T13" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>8.654587268330266E-2</v>
       </c>
       <c r="U13" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>4.8591378096403126E-3</v>
       </c>
       <c r="V13" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+        <v>8.6607582095162838E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f>'Proximal Validation (single)'!A14</f>
         <v>0.4</v>
@@ -4654,29 +4771,39 @@
         <f>'Proximal Validation (single)'!M14</f>
         <v>-0.17468151450157199</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="10"/>
+      <c r="N14" s="9">
+        <v>0.36396812880457791</v>
+      </c>
+      <c r="O14" s="9">
+        <v>5.1899400330226157E-2</v>
+      </c>
+      <c r="P14" s="9">
+        <v>3.6659592917673365</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>1.5894261036591588</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1.3488739619692586E-4</v>
+      </c>
       <c r="S14" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>3.6031871195422116E-2</v>
       </c>
       <c r="T14" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>4.8100599669773848E-2</v>
       </c>
       <c r="U14" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>9.5929176733644539E-4</v>
       </c>
       <c r="V14" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.8426103659158866E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f>'Proximal Validation (single)'!A15</f>
         <v>0.7</v>
@@ -4729,29 +4856,39 @@
         <f>'Proximal Validation (single)'!M15</f>
         <v>-0.33820247650146501</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="10"/>
+      <c r="N15" s="9">
+        <v>0.70644217184042479</v>
+      </c>
+      <c r="O15" s="9">
+        <v>5.1514762286886832E-2</v>
+      </c>
+      <c r="P15" s="9">
+        <v>3.6655388603770862</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>1.6118385621667133</v>
+      </c>
+      <c r="R15" s="10">
+        <v>5.1611100815983748E-4</v>
+      </c>
       <c r="S15" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>6.4421718404248374E-3</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>4.8485237713113173E-2</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>5.3886037708616996E-4</v>
       </c>
       <c r="V15" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.0838562166713333E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f>'Proximal Validation (single)'!A16</f>
         <v>0.4</v>
@@ -4804,29 +4941,39 @@
         <f>'Proximal Validation (single)'!M16</f>
         <v>-0.16520524024963401</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="10"/>
+      <c r="N16" s="9">
+        <v>0.34645629427592745</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0.10226963684187816</v>
+      </c>
+      <c r="P16" s="9">
+        <v>3.6749292127814588</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1.6505159308144088</v>
+      </c>
+      <c r="R16" s="10">
+        <v>2.2799264723760262E-4</v>
+      </c>
       <c r="S16" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>5.3543705724072577E-2</v>
       </c>
       <c r="T16" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>5.7730363158121842E-2</v>
       </c>
       <c r="U16" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>9.9292127814587516E-3</v>
       </c>
       <c r="V16" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>7.9515930814408886E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <f>'Proximal Validation (single)'!A17</f>
         <v>0.3</v>
@@ -4879,26 +5026,36 @@
         <f>'Proximal Validation (single)'!M17</f>
         <v>-0.10984055697917899</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="10"/>
+      <c r="N17" s="9">
+        <v>0.23175799741967446</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0.11527950093193579</v>
+      </c>
+      <c r="P17" s="9">
+        <v>3.6658474804100769</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>1.5791992740934826</v>
+      </c>
+      <c r="R17" s="10">
+        <v>1.1344985095968117E-4</v>
+      </c>
       <c r="S17" s="8">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>6.8242002580325534E-2</v>
       </c>
       <c r="T17" s="8">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>6.4720499068064208E-2</v>
       </c>
       <c r="U17" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>8.4748041007687291E-4</v>
       </c>
       <c r="V17" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>8.1992740934826447E-3</v>
       </c>
     </row>
   </sheetData>
@@ -4915,11 +5072,1914 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106BFA6D-FE6F-4AF3-8379-A44BC5ECB9FF}">
+  <dimension ref="A1:Z17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <f>'Proximal Validation (single)'!A3</f>
+        <v>0.3</v>
+      </c>
+      <c r="B3" s="9">
+        <f>'Proximal Validation (single)'!B3</f>
+        <v>0.08</v>
+      </c>
+      <c r="C3" s="9">
+        <f>'Proximal Validation (single)'!C3</f>
+        <v>1.571</v>
+      </c>
+      <c r="D3" s="9">
+        <f>'Proximal Validation (single)'!D3</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E3" s="9">
+        <f>'Proximal Validation (single)'!E3</f>
+        <v>1.4</v>
+      </c>
+      <c r="F3" s="9">
+        <f>'Proximal Validation (single)'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <f>'Proximal Validation (single)'!G3</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <f>'Proximal Validation (single)'!H3</f>
+        <v>-1.5595351578667801E-4</v>
+      </c>
+      <c r="I3" s="9">
+        <f>'Proximal Validation (single)'!I3</f>
+        <v>-3.4215424209833097E-2</v>
+      </c>
+      <c r="J3" s="9">
+        <f>'Proximal Validation (single)'!J3</f>
+        <v>-1.4112447388470199E-7</v>
+      </c>
+      <c r="K3" s="9">
+        <f>'Proximal Validation (single)'!K3</f>
+        <v>0.19788618385791801</v>
+      </c>
+      <c r="L3" s="9">
+        <f>'Proximal Validation (single)'!L3</f>
+        <v>-3.1988471746444702E-3</v>
+      </c>
+      <c r="M3" s="9">
+        <f>'Proximal Validation (single)'!M3</f>
+        <v>0.198836579918861</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0.23105392938065236</v>
+      </c>
+      <c r="O3" s="9">
+        <v>6.3315371064735601E-2</v>
+      </c>
+      <c r="P3" s="9">
+        <v>1.5408993982454715</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>1.1740794994170503</v>
+      </c>
+      <c r="R3" s="10">
+        <v>5.1399354462416556E-4</v>
+      </c>
+      <c r="S3" s="8">
+        <f>ABS(N3-A3)</f>
+        <v>6.8946070619347627E-2</v>
+      </c>
+      <c r="T3" s="8">
+        <f t="shared" ref="T3:V17" si="0">ABS(O3-B3)</f>
+        <v>1.6684628935264401E-2</v>
+      </c>
+      <c r="U3" s="8">
+        <f t="shared" si="0"/>
+        <v>3.0100601754528444E-2</v>
+      </c>
+      <c r="V3" s="8">
+        <f t="shared" si="0"/>
+        <v>0.38907949941705022</v>
+      </c>
+      <c r="W3" s="9">
+        <f>AVERAGE(S3:S17)</f>
+        <v>6.366645912806794E-2</v>
+      </c>
+      <c r="X3" s="9">
+        <f t="shared" ref="X3:Z3" si="1">AVERAGE(T3:T17)</f>
+        <v>2.363298510729496E-2</v>
+      </c>
+      <c r="Y3" s="9">
+        <f>AVERAGE(U3:U17)</f>
+        <v>3.3476689797409004E-2</v>
+      </c>
+      <c r="Z3" s="9">
+        <f t="shared" si="1"/>
+        <v>0.16094337924390839</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <f>'Proximal Validation (single)'!A4</f>
+        <v>0.4</v>
+      </c>
+      <c r="B4" s="9">
+        <f>'Proximal Validation (single)'!B4</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C4" s="9">
+        <f>'Proximal Validation (single)'!C4</f>
+        <v>1.571</v>
+      </c>
+      <c r="D4" s="9">
+        <f>'Proximal Validation (single)'!D4</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E4" s="9">
+        <f>'Proximal Validation (single)'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <f>'Proximal Validation (single)'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <f>'Proximal Validation (single)'!G4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <f>'Proximal Validation (single)'!H4</f>
+        <v>-2.4353998014703401E-4</v>
+      </c>
+      <c r="I4" s="9">
+        <f>'Proximal Validation (single)'!I4</f>
+        <v>-5.8889582753181499E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <f>'Proximal Validation (single)'!J4</f>
+        <v>-5.9254060033708797E-5</v>
+      </c>
+      <c r="K4" s="9">
+        <f>'Proximal Validation (single)'!K4</f>
+        <v>0.25050288438797003</v>
+      </c>
+      <c r="L4" s="9">
+        <f>'Proximal Validation (single)'!L4</f>
+        <v>9.8302215337753296E-4</v>
+      </c>
+      <c r="M4" s="9">
+        <f>'Proximal Validation (single)'!M4</f>
+        <v>0.25498384237289401</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0.30354623382092344</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0.12647640102435134</v>
+      </c>
+      <c r="P4" s="9">
+        <v>1.5270848513602746</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>1.008157100822312</v>
+      </c>
+      <c r="R4" s="10">
+        <v>5.7403401798239949E-4</v>
+      </c>
+      <c r="S4" s="8">
+        <f t="shared" ref="S4:S17" si="2">ABS(N4-A4)</f>
+        <v>9.6453766179076583E-2</v>
+      </c>
+      <c r="T4" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3523598975648671E-2</v>
+      </c>
+      <c r="U4" s="8">
+        <f t="shared" si="0"/>
+        <v>4.3915148639725343E-2</v>
+      </c>
+      <c r="V4" s="8">
+        <f t="shared" si="0"/>
+        <v>0.22315710082231199</v>
+      </c>
+      <c r="Y4">
+        <f>DEGREES(Y3)</f>
+        <v>1.9180730374601989</v>
+      </c>
+      <c r="Z4">
+        <f>DEGREES(Z3)</f>
+        <v>9.2213763712493648</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <f>'Proximal Validation (single)'!A5</f>
+        <v>0.6</v>
+      </c>
+      <c r="B5" s="9">
+        <f>'Proximal Validation (single)'!B5</f>
+        <v>0.16</v>
+      </c>
+      <c r="C5" s="9">
+        <f>'Proximal Validation (single)'!C5</f>
+        <v>1.571</v>
+      </c>
+      <c r="D5" s="9">
+        <f>'Proximal Validation (single)'!D5</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E5" s="9">
+        <f>'Proximal Validation (single)'!E5</f>
+        <v>1.4</v>
+      </c>
+      <c r="F5" s="9">
+        <f>'Proximal Validation (single)'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <f>'Proximal Validation (single)'!G5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <f>'Proximal Validation (single)'!H5</f>
+        <v>2.2863354533910799E-3</v>
+      </c>
+      <c r="I5" s="9">
+        <f>'Proximal Validation (single)'!I5</f>
+        <v>-0.11987078934907899</v>
+      </c>
+      <c r="J5" s="9">
+        <f>'Proximal Validation (single)'!J5</f>
+        <v>-6.9630080834031096E-3</v>
+      </c>
+      <c r="K5" s="9">
+        <f>'Proximal Validation (single)'!K5</f>
+        <v>0.31022596359252902</v>
+      </c>
+      <c r="L5" s="9">
+        <f>'Proximal Validation (single)'!L5</f>
+        <v>-2.3233078420162201E-2</v>
+      </c>
+      <c r="M5" s="9">
+        <f>'Proximal Validation (single)'!M5</f>
+        <v>0.50102174282073997</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0.55319463501294608</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0.15886634238059388</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1.6479884706601358</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0.87602659492882007</v>
+      </c>
+      <c r="R5" s="10">
+        <v>6.0067033260650308E-4</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" si="2"/>
+        <v>4.6805364987053899E-2</v>
+      </c>
+      <c r="T5" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1336576194061199E-3</v>
+      </c>
+      <c r="U5" s="8">
+        <f t="shared" si="0"/>
+        <v>7.698847066013581E-2</v>
+      </c>
+      <c r="V5" s="8">
+        <f t="shared" si="0"/>
+        <v>9.1026594928820037E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <f>'Proximal Validation (single)'!A6</f>
+        <v>0.4</v>
+      </c>
+      <c r="B6" s="9">
+        <f>'Proximal Validation (single)'!B6</f>
+        <v>0.06</v>
+      </c>
+      <c r="C6" s="9">
+        <f>'Proximal Validation (single)'!C6</f>
+        <v>1.571</v>
+      </c>
+      <c r="D6" s="9">
+        <f>'Proximal Validation (single)'!D6</f>
+        <v>1.571</v>
+      </c>
+      <c r="E6" s="9">
+        <f>'Proximal Validation (single)'!E6</f>
+        <v>1.4</v>
+      </c>
+      <c r="F6" s="9">
+        <f>'Proximal Validation (single)'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <f>'Proximal Validation (single)'!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <f>'Proximal Validation (single)'!H6</f>
+        <v>6.5225898288190397E-4</v>
+      </c>
+      <c r="I6" s="9">
+        <f>'Proximal Validation (single)'!I6</f>
+        <v>-6.1197262257337598E-2</v>
+      </c>
+      <c r="J6" s="9">
+        <f>'Proximal Validation (single)'!J6</f>
+        <v>-8.9818926062434901E-4</v>
+      </c>
+      <c r="K6" s="9">
+        <f>'Proximal Validation (single)'!K6</f>
+        <v>-1.97219010442495E-3</v>
+      </c>
+      <c r="L6" s="9">
+        <f>'Proximal Validation (single)'!L6</f>
+        <v>-5.79428672790527E-3</v>
+      </c>
+      <c r="M6" s="9">
+        <f>'Proximal Validation (single)'!M6</f>
+        <v>0.38675421476364102</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0.42174994714766129</v>
+      </c>
+      <c r="O6" s="9">
+        <v>5.8386275600091159E-2</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1.546823577038891</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1.8042458180028351</v>
+      </c>
+      <c r="R6" s="10">
+        <v>5.2720557749483352E-4</v>
+      </c>
+      <c r="S6" s="8">
+        <f t="shared" si="2"/>
+        <v>2.1749947147661264E-2</v>
+      </c>
+      <c r="T6" s="8">
+        <f t="shared" si="0"/>
+        <v>1.6137243999088391E-3</v>
+      </c>
+      <c r="U6" s="8">
+        <f t="shared" si="0"/>
+        <v>2.4176422961109001E-2</v>
+      </c>
+      <c r="V6" s="8">
+        <f t="shared" si="0"/>
+        <v>0.23324581800283517</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <f>'Proximal Validation (single)'!A7</f>
+        <v>0.8</v>
+      </c>
+      <c r="B7" s="9">
+        <f>'Proximal Validation (single)'!B7</f>
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="9">
+        <f>'Proximal Validation (single)'!C7</f>
+        <v>1.571</v>
+      </c>
+      <c r="D7" s="9">
+        <f>'Proximal Validation (single)'!D7</f>
+        <v>1.571</v>
+      </c>
+      <c r="E7" s="9">
+        <f>'Proximal Validation (single)'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <f>'Proximal Validation (single)'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <f>'Proximal Validation (single)'!G7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <f>'Proximal Validation (single)'!H7</f>
+        <v>-4.06092498451471E-4</v>
+      </c>
+      <c r="I7" s="9">
+        <f>'Proximal Validation (single)'!I7</f>
+        <v>-0.15244589745998399</v>
+      </c>
+      <c r="J7" s="9">
+        <f>'Proximal Validation (single)'!J7</f>
+        <v>-1.21209200005978E-3</v>
+      </c>
+      <c r="K7" s="9">
+        <f>'Proximal Validation (single)'!K7</f>
+        <v>-0.117412149906158</v>
+      </c>
+      <c r="L7" s="9">
+        <f>'Proximal Validation (single)'!L7</f>
+        <v>-2.6462823152542101E-3</v>
+      </c>
+      <c r="M7" s="9">
+        <f>'Proximal Validation (single)'!M7</f>
+        <v>0.85134243965148904</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0.90018007462909155</v>
+      </c>
+      <c r="O7" s="9">
+        <v>8.3124801847529198E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <v>1.5603917255226749</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.6744126666225396</v>
+      </c>
+      <c r="R7" s="10">
+        <v>5.7935679095468819E-4</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="2"/>
+        <v>0.10018007462909151</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" si="0"/>
+        <v>3.1248018475291961E-3</v>
+      </c>
+      <c r="U7" s="8">
+        <f t="shared" si="0"/>
+        <v>1.0608274477325041E-2</v>
+      </c>
+      <c r="V7" s="8">
+        <f t="shared" si="0"/>
+        <v>0.10341266662253967</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" s="9">
+        <f>'Proximal Validation (single)'!A8</f>
+        <v>0.7</v>
+      </c>
+      <c r="B8" s="9">
+        <f>'Proximal Validation (single)'!B8</f>
+        <v>0.16</v>
+      </c>
+      <c r="C8" s="9">
+        <f>'Proximal Validation (single)'!C8</f>
+        <v>1.571</v>
+      </c>
+      <c r="D8" s="9">
+        <f>'Proximal Validation (single)'!D8</f>
+        <v>1.571</v>
+      </c>
+      <c r="E8" s="9">
+        <f>'Proximal Validation (single)'!E8</f>
+        <v>1.4</v>
+      </c>
+      <c r="F8" s="9">
+        <f>'Proximal Validation (single)'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <f>'Proximal Validation (single)'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <f>'Proximal Validation (single)'!H8</f>
+        <v>5.05214463919401E-3</v>
+      </c>
+      <c r="I8" s="9">
+        <f>'Proximal Validation (single)'!I8</f>
+        <v>-0.157537400722504</v>
+      </c>
+      <c r="J8" s="9">
+        <f>'Proximal Validation (single)'!J8</f>
+        <v>-6.2086973339319203E-3</v>
+      </c>
+      <c r="K8" s="9">
+        <f>'Proximal Validation (single)'!K8</f>
+        <v>-0.29486876726150502</v>
+      </c>
+      <c r="L8" s="9">
+        <f>'Proximal Validation (single)'!L8</f>
+        <v>-2.80796959996223E-2</v>
+      </c>
+      <c r="M8" s="9">
+        <f>'Proximal Validation (single)'!M8</f>
+        <v>0.56537818908691395</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0.71448281487836196</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0.15370117008511555</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1.5741849850195675</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>1.7107256519224883</v>
+      </c>
+      <c r="R8" s="10">
+        <v>6.4018377241843E-4</v>
+      </c>
+      <c r="S8" s="8">
+        <f t="shared" si="2"/>
+        <v>1.4482814878362005E-2</v>
+      </c>
+      <c r="T8" s="8">
+        <f t="shared" si="0"/>
+        <v>6.2988299148844518E-3</v>
+      </c>
+      <c r="U8" s="8">
+        <f t="shared" si="0"/>
+        <v>3.1849850195675433E-3</v>
+      </c>
+      <c r="V8" s="8">
+        <f t="shared" si="0"/>
+        <v>0.13972565192248831</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" s="9">
+        <f>'Proximal Validation (single)'!A9</f>
+        <v>0.7</v>
+      </c>
+      <c r="B9" s="9">
+        <f>'Proximal Validation (single)'!B9</f>
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="9">
+        <f>'Proximal Validation (single)'!C9</f>
+        <v>1.571</v>
+      </c>
+      <c r="D9" s="9">
+        <f>'Proximal Validation (single)'!D9</f>
+        <v>1.571</v>
+      </c>
+      <c r="E9" s="9">
+        <f>'Proximal Validation (single)'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <f>'Proximal Validation (single)'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <f>'Proximal Validation (single)'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <f>'Proximal Validation (single)'!H9</f>
+        <v>3.71134956367314E-5</v>
+      </c>
+      <c r="I9" s="9">
+        <f>'Proximal Validation (single)'!I9</f>
+        <v>-0.19372102618217499</v>
+      </c>
+      <c r="J9" s="9">
+        <f>'Proximal Validation (single)'!J9</f>
+        <v>-2.1289892029017201E-3</v>
+      </c>
+      <c r="K9" s="9">
+        <f>'Proximal Validation (single)'!K9</f>
+        <v>-0.41201990842819203</v>
+      </c>
+      <c r="L9" s="9">
+        <f>'Proximal Validation (single)'!L9</f>
+        <v>-1.1864490807056401E-3</v>
+      </c>
+      <c r="M9" s="9">
+        <f>'Proximal Validation (single)'!M9</f>
+        <v>0.55889892578125</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0.78293114450246792</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.18958412823281595</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1.5594292973769728</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>1.5755792279152727</v>
+      </c>
+      <c r="R9" s="10">
+        <v>6.8362144708908009E-4</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="2"/>
+        <v>8.2931144502467968E-2</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" si="0"/>
+        <v>1.0415871767184059E-2</v>
+      </c>
+      <c r="U9" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1570702623027174E-2</v>
+      </c>
+      <c r="V9" s="8">
+        <f t="shared" si="0"/>
+        <v>4.5792279152727655E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" s="9">
+        <f>'Proximal Validation (single)'!A10</f>
+        <v>0.7</v>
+      </c>
+      <c r="B10" s="9">
+        <f>'Proximal Validation (single)'!B10</f>
+        <v>0.06</v>
+      </c>
+      <c r="C10" s="9">
+        <f>'Proximal Validation (single)'!C10</f>
+        <v>3.665</v>
+      </c>
+      <c r="D10" s="9">
+        <f>'Proximal Validation (single)'!D10</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E10" s="9">
+        <f>'Proximal Validation (single)'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <f>'Proximal Validation (single)'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <f>'Proximal Validation (single)'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <f>'Proximal Validation (single)'!H10</f>
+        <v>-8.9350854977965398E-4</v>
+      </c>
+      <c r="I10" s="9">
+        <f>'Proximal Validation (single)'!I10</f>
+        <v>4.2732272297143901E-2</v>
+      </c>
+      <c r="J10" s="9">
+        <f>'Proximal Validation (single)'!J10</f>
+        <v>-7.74873793125153E-2</v>
+      </c>
+      <c r="K10" s="9">
+        <f>'Proximal Validation (single)'!K10</f>
+        <v>0.62493914365768399</v>
+      </c>
+      <c r="L10" s="9">
+        <f>'Proximal Validation (single)'!L10</f>
+        <v>-0.52349442243576105</v>
+      </c>
+      <c r="M10" s="9">
+        <f>'Proximal Validation (single)'!M10</f>
+        <v>-0.28826642036437999</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0.76728977148308719</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0.10118577138133467</v>
+      </c>
+      <c r="P10" s="9">
+        <v>3.6290071907384194</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0.7100076987975219</v>
+      </c>
+      <c r="R10" s="10">
+        <v>1.6757707583499497E-4</v>
+      </c>
+      <c r="S10" s="8">
+        <f t="shared" si="2"/>
+        <v>6.7289771483087235E-2</v>
+      </c>
+      <c r="T10" s="8">
+        <f t="shared" si="0"/>
+        <v>4.1185771381334668E-2</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" si="0"/>
+        <v>3.5992809261580661E-2</v>
+      </c>
+      <c r="V10" s="8">
+        <f t="shared" si="0"/>
+        <v>7.4992301202478129E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="9">
+        <f>'Proximal Validation (single)'!A11</f>
+        <v>0.6</v>
+      </c>
+      <c r="B11" s="9">
+        <f>'Proximal Validation (single)'!B11</f>
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="9">
+        <f>'Proximal Validation (single)'!C11</f>
+        <v>3.665</v>
+      </c>
+      <c r="D11" s="9">
+        <f>'Proximal Validation (single)'!D11</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E11" s="9">
+        <f>'Proximal Validation (single)'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <f>'Proximal Validation (single)'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <f>'Proximal Validation (single)'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <f>'Proximal Validation (single)'!H11</f>
+        <v>-8.9688366279006004E-4</v>
+      </c>
+      <c r="I11" s="9">
+        <f>'Proximal Validation (single)'!I11</f>
+        <v>4.1764143854379703E-2</v>
+      </c>
+      <c r="J11" s="9">
+        <f>'Proximal Validation (single)'!J11</f>
+        <v>-7.7566295862197904E-2</v>
+      </c>
+      <c r="K11" s="9">
+        <f>'Proximal Validation (single)'!K11</f>
+        <v>0.45929118990898099</v>
+      </c>
+      <c r="L11" s="9">
+        <f>'Proximal Validation (single)'!L11</f>
+        <v>-0.41274711489677401</v>
+      </c>
+      <c r="M11" s="9">
+        <f>'Proximal Validation (single)'!M11</f>
+        <v>-0.223745286464691</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0.56310084049764919</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0.17142791803564372</v>
+      </c>
+      <c r="P11" s="9">
+        <v>3.616903655823891</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0.64182346693340264</v>
+      </c>
+      <c r="R11" s="10">
+        <v>1.6346024191416563E-4</v>
+      </c>
+      <c r="S11" s="8">
+        <f t="shared" si="2"/>
+        <v>3.6899159502350787E-2</v>
+      </c>
+      <c r="T11" s="8">
+        <f t="shared" si="0"/>
+        <v>7.1427918035643717E-2</v>
+      </c>
+      <c r="U11" s="8">
+        <f t="shared" si="0"/>
+        <v>4.8096344176109085E-2</v>
+      </c>
+      <c r="V11" s="8">
+        <f t="shared" si="0"/>
+        <v>0.14317653306659739</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" s="9">
+        <f>'Proximal Validation (single)'!A12</f>
+        <v>0.8</v>
+      </c>
+      <c r="B12" s="9">
+        <f>'Proximal Validation (single)'!B12</f>
+        <v>0.18</v>
+      </c>
+      <c r="C12" s="9">
+        <f>'Proximal Validation (single)'!C12</f>
+        <v>3.665</v>
+      </c>
+      <c r="D12" s="9">
+        <f>'Proximal Validation (single)'!D12</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E12" s="9">
+        <f>'Proximal Validation (single)'!E12</f>
+        <v>1.4</v>
+      </c>
+      <c r="F12" s="9">
+        <f>'Proximal Validation (single)'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <f>'Proximal Validation (single)'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <f>'Proximal Validation (single)'!H12</f>
+        <v>-5.51847275346518E-4</v>
+      </c>
+      <c r="I12" s="9">
+        <f>'Proximal Validation (single)'!I12</f>
+        <v>6.6554106771945995E-2</v>
+      </c>
+      <c r="J12" s="9">
+        <f>'Proximal Validation (single)'!J12</f>
+        <v>-0.119616024196148</v>
+      </c>
+      <c r="K12" s="9">
+        <f>'Proximal Validation (single)'!K12</f>
+        <v>0.49095398187637301</v>
+      </c>
+      <c r="L12" s="9">
+        <f>'Proximal Validation (single)'!L12</f>
+        <v>-0.47584062814712502</v>
+      </c>
+      <c r="M12" s="9">
+        <f>'Proximal Validation (single)'!M12</f>
+        <v>-0.25870200991630599</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0.64365955382631657</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P12" s="9">
+        <v>3.6268573343472257</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0.65319231400842237</v>
+      </c>
+      <c r="R12" s="10">
+        <v>6.3125350598853918E-4</v>
+      </c>
+      <c r="S12" s="8">
+        <f t="shared" si="2"/>
+        <v>0.15634044617368348</v>
+      </c>
+      <c r="T12" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U12" s="8">
+        <f t="shared" si="0"/>
+        <v>3.8142665652774355E-2</v>
+      </c>
+      <c r="V12" s="8">
+        <f t="shared" si="0"/>
+        <v>0.13180768599157766</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" s="9">
+        <f>'Proximal Validation (single)'!A13</f>
+        <v>0.4</v>
+      </c>
+      <c r="B13" s="9">
+        <f>'Proximal Validation (single)'!B13</f>
+        <v>0.2</v>
+      </c>
+      <c r="C13" s="9">
+        <f>'Proximal Validation (single)'!C13</f>
+        <v>3.665</v>
+      </c>
+      <c r="D13" s="9">
+        <f>'Proximal Validation (single)'!D13</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E13" s="9">
+        <f>'Proximal Validation (single)'!E13</f>
+        <v>1.4</v>
+      </c>
+      <c r="F13" s="9">
+        <f>'Proximal Validation (single)'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <f>'Proximal Validation (single)'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <f>'Proximal Validation (single)'!H13</f>
+        <v>-3.2309396192431499E-4</v>
+      </c>
+      <c r="I13" s="9">
+        <f>'Proximal Validation (single)'!I13</f>
+        <v>3.5572569817304597E-2</v>
+      </c>
+      <c r="J13" s="9">
+        <f>'Proximal Validation (single)'!J13</f>
+        <v>-6.1782382428646102E-2</v>
+      </c>
+      <c r="K13" s="9">
+        <f>'Proximal Validation (single)'!K13</f>
+        <v>0.27096122503280601</v>
+      </c>
+      <c r="L13" s="9">
+        <f>'Proximal Validation (single)'!L13</f>
+        <v>-0.21531303226947801</v>
+      </c>
+      <c r="M13" s="9">
+        <f>'Proximal Validation (single)'!M13</f>
+        <v>-0.122712507843971</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0.27804919690398439</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P13" s="9">
+        <v>3.6240274935161647</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0.88413850903099622</v>
+      </c>
+      <c r="R13" s="10">
+        <v>7.5096690558036205E-4</v>
+      </c>
+      <c r="S13" s="8">
+        <f t="shared" si="2"/>
+        <v>0.12195080309601564</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="0"/>
+        <v>4.0972506483835325E-2</v>
+      </c>
+      <c r="V13" s="8">
+        <f t="shared" si="0"/>
+        <v>9.9138509030996191E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" s="9">
+        <f>'Proximal Validation (single)'!A14</f>
+        <v>0.4</v>
+      </c>
+      <c r="B14" s="9">
+        <f>'Proximal Validation (single)'!B14</f>
+        <v>0.1</v>
+      </c>
+      <c r="C14" s="9">
+        <f>'Proximal Validation (single)'!C14</f>
+        <v>3.665</v>
+      </c>
+      <c r="D14" s="9">
+        <f>'Proximal Validation (single)'!D14</f>
+        <v>1.571</v>
+      </c>
+      <c r="E14" s="9">
+        <f>'Proximal Validation (single)'!E14</f>
+        <v>1.4</v>
+      </c>
+      <c r="F14" s="9">
+        <f>'Proximal Validation (single)'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <f>'Proximal Validation (single)'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <f>'Proximal Validation (single)'!H14</f>
+        <v>-7.1692815981805303E-4</v>
+      </c>
+      <c r="I14" s="9">
+        <f>'Proximal Validation (single)'!I14</f>
+        <v>3.56008112430573E-2</v>
+      </c>
+      <c r="J14" s="9">
+        <f>'Proximal Validation (single)'!J14</f>
+        <v>-6.2020469456911101E-2</v>
+      </c>
+      <c r="K14" s="9">
+        <f>'Proximal Validation (single)'!K14</f>
+        <v>-6.5964758396148699E-3</v>
+      </c>
+      <c r="L14" s="9">
+        <f>'Proximal Validation (single)'!L14</f>
+        <v>-0.30639430880546598</v>
+      </c>
+      <c r="M14" s="9">
+        <f>'Proximal Validation (single)'!M14</f>
+        <v>-0.17468151450157199</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0.35327471561838264</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0.16941225557212655</v>
+      </c>
+      <c r="P14" s="9">
+        <v>3.6311749950517691</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>1.7682158233044356</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1.5738096474029786E-4</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" si="2"/>
+        <v>4.6725284381617382E-2</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" si="0"/>
+        <v>6.9412255572126547E-2</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" si="0"/>
+        <v>3.382500494823093E-2</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.19721582330443566</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A15" s="9">
+        <f>'Proximal Validation (single)'!A15</f>
+        <v>0.7</v>
+      </c>
+      <c r="B15" s="9">
+        <f>'Proximal Validation (single)'!B15</f>
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="9">
+        <f>'Proximal Validation (single)'!C15</f>
+        <v>3.665</v>
+      </c>
+      <c r="D15" s="9">
+        <f>'Proximal Validation (single)'!D15</f>
+        <v>1.571</v>
+      </c>
+      <c r="E15" s="9">
+        <f>'Proximal Validation (single)'!E15</f>
+        <v>1.4</v>
+      </c>
+      <c r="F15" s="9">
+        <f>'Proximal Validation (single)'!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <f>'Proximal Validation (single)'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <f>'Proximal Validation (single)'!H15</f>
+        <v>-1.24058220535517E-3</v>
+      </c>
+      <c r="I15" s="9">
+        <f>'Proximal Validation (single)'!I15</f>
+        <v>6.9012217223644298E-2</v>
+      </c>
+      <c r="J15" s="9">
+        <f>'Proximal Validation (single)'!J15</f>
+        <v>-0.119697146117687</v>
+      </c>
+      <c r="K15" s="9">
+        <f>'Proximal Validation (single)'!K15</f>
+        <v>-5.5351331830024698E-2</v>
+      </c>
+      <c r="L15" s="9">
+        <f>'Proximal Validation (single)'!L15</f>
+        <v>-0.59383064508438099</v>
+      </c>
+      <c r="M15" s="9">
+        <f>'Proximal Validation (single)'!M15</f>
+        <v>-0.33820247650146501</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0.68360963686820286</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0.13967371816049376</v>
+      </c>
+      <c r="P15" s="9">
+        <v>3.6456463693358034</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>1.5578424581286345</v>
+      </c>
+      <c r="R15" s="10">
+        <v>1.6558110999764192E-4</v>
+      </c>
+      <c r="S15" s="8">
+        <f t="shared" si="2"/>
+        <v>1.6390363131797092E-2</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" si="0"/>
+        <v>3.9673718160493754E-2</v>
+      </c>
+      <c r="U15" s="8">
+        <f t="shared" si="0"/>
+        <v>1.9353630664196597E-2</v>
+      </c>
+      <c r="V15" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3157541871365419E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" s="9">
+        <f>'Proximal Validation (single)'!A16</f>
+        <v>0.4</v>
+      </c>
+      <c r="B16" s="9">
+        <f>'Proximal Validation (single)'!B16</f>
+        <v>0.16</v>
+      </c>
+      <c r="C16" s="9">
+        <f>'Proximal Validation (single)'!C16</f>
+        <v>3.665</v>
+      </c>
+      <c r="D16" s="9">
+        <f>'Proximal Validation (single)'!D16</f>
+        <v>1.571</v>
+      </c>
+      <c r="E16" s="9">
+        <f>'Proximal Validation (single)'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <f>'Proximal Validation (single)'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <f>'Proximal Validation (single)'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <f>'Proximal Validation (single)'!H16</f>
+        <v>-7.1821291930973497E-4</v>
+      </c>
+      <c r="I16" s="9">
+        <f>'Proximal Validation (single)'!I16</f>
+        <v>4.6037148684263202E-2</v>
+      </c>
+      <c r="J16" s="9">
+        <f>'Proximal Validation (single)'!J16</f>
+        <v>-7.8464329242706299E-2</v>
+      </c>
+      <c r="K16" s="9">
+        <f>'Proximal Validation (single)'!K16</f>
+        <v>-7.8753150999546107E-2</v>
+      </c>
+      <c r="L16" s="9">
+        <f>'Proximal Validation (single)'!L16</f>
+        <v>-0.286407381296158</v>
+      </c>
+      <c r="M16" s="9">
+        <f>'Proximal Validation (single)'!M16</f>
+        <v>-0.16520524024963401</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0.3687448760989343</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="9">
+        <v>3.6353507071935867</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1.7685383613390888</v>
+      </c>
+      <c r="R16" s="10">
+        <v>2.6494774957646402E-4</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" si="2"/>
+        <v>3.1255123901065718E-2</v>
+      </c>
+      <c r="T16" s="8">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" si="0"/>
+        <v>2.9649292806413374E-2</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" si="0"/>
+        <v>0.19753836133908886</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="9">
+        <f>'Proximal Validation (single)'!A17</f>
+        <v>0.3</v>
+      </c>
+      <c r="B17" s="9">
+        <f>'Proximal Validation (single)'!B17</f>
+        <v>0.18</v>
+      </c>
+      <c r="C17" s="9">
+        <f>'Proximal Validation (single)'!C17</f>
+        <v>3.665</v>
+      </c>
+      <c r="D17" s="9">
+        <f>'Proximal Validation (single)'!D17</f>
+        <v>1.571</v>
+      </c>
+      <c r="E17" s="9">
+        <f>'Proximal Validation (single)'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <f>'Proximal Validation (single)'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <f>'Proximal Validation (single)'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <f>'Proximal Validation (single)'!H17</f>
+        <v>-6.2177400104701497E-4</v>
+      </c>
+      <c r="I17" s="9">
+        <f>'Proximal Validation (single)'!I17</f>
+        <v>3.2626789063215297E-2</v>
+      </c>
+      <c r="J17" s="9">
+        <f>'Proximal Validation (single)'!J17</f>
+        <v>-5.72014674544334E-2</v>
+      </c>
+      <c r="K17" s="9">
+        <f>'Proximal Validation (single)'!K17</f>
+        <v>-2.7179472148418399E-2</v>
+      </c>
+      <c r="L17" s="9">
+        <f>'Proximal Validation (single)'!L17</f>
+        <v>-0.194883912801743</v>
+      </c>
+      <c r="M17" s="9">
+        <f>'Proximal Validation (single)'!M17</f>
+        <v>-0.10984055697917899</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0.25340324769165912</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P17" s="9">
+        <v>3.6094265131674237</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>1.9438973732207685</v>
+      </c>
+      <c r="R17" s="10">
+        <v>5.2603374884629907E-4</v>
+      </c>
+      <c r="S17" s="8">
+        <f t="shared" si="2"/>
+        <v>4.6596752308340872E-2</v>
+      </c>
+      <c r="T17" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U17" s="8">
+        <f t="shared" si="0"/>
+        <v>5.5573486832576346E-2</v>
+      </c>
+      <c r="V17" s="8">
+        <f t="shared" si="0"/>
+        <v>0.37289737322076855</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="W1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830C3293-DA71-4012-9049-749D5DDC24A3}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="29">
+        <v>-1.5595351578667801E-4</v>
+      </c>
+      <c r="B1" s="29">
+        <v>-3.4215424209833097E-2</v>
+      </c>
+      <c r="C1" s="29">
+        <v>-1.4112447388470199E-7</v>
+      </c>
+      <c r="D1" s="29">
+        <v>0.19788618385791801</v>
+      </c>
+      <c r="E1" s="29">
+        <v>-3.1988471746444702E-3</v>
+      </c>
+      <c r="F1" s="29">
+        <v>0.198836579918861</v>
+      </c>
+      <c r="G1" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H1" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="29">
+        <v>-2.4353998014703401E-4</v>
+      </c>
+      <c r="B2" s="29">
+        <v>-5.8889582753181499E-2</v>
+      </c>
+      <c r="C2" s="29">
+        <v>-5.9254060033708797E-5</v>
+      </c>
+      <c r="D2" s="29">
+        <v>0.25050288438797003</v>
+      </c>
+      <c r="E2" s="29">
+        <v>9.8302215337753296E-4</v>
+      </c>
+      <c r="F2" s="29">
+        <v>0.25498384237289401</v>
+      </c>
+      <c r="G2" s="29">
+        <v>0</v>
+      </c>
+      <c r="H2" s="29">
+        <v>0</v>
+      </c>
+      <c r="I2" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="29">
+        <v>2.2863354533910799E-3</v>
+      </c>
+      <c r="B3" s="29">
+        <v>-0.11987078934907899</v>
+      </c>
+      <c r="C3" s="29">
+        <v>-6.9630080834031096E-3</v>
+      </c>
+      <c r="D3" s="29">
+        <v>0.31022596359252902</v>
+      </c>
+      <c r="E3" s="29">
+        <v>-2.3233078420162201E-2</v>
+      </c>
+      <c r="F3" s="29">
+        <v>0.50102174282073997</v>
+      </c>
+      <c r="G3" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H3" s="29">
+        <v>0</v>
+      </c>
+      <c r="I3" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="29">
+        <v>6.5225898288190397E-4</v>
+      </c>
+      <c r="B4" s="29">
+        <v>-6.1197262257337598E-2</v>
+      </c>
+      <c r="C4" s="29">
+        <v>-8.9818926062434901E-4</v>
+      </c>
+      <c r="D4" s="29">
+        <v>-1.97219010442495E-3</v>
+      </c>
+      <c r="E4" s="29">
+        <v>-5.79428672790527E-3</v>
+      </c>
+      <c r="F4" s="29">
+        <v>0.38675421476364102</v>
+      </c>
+      <c r="G4" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H4" s="29">
+        <v>0</v>
+      </c>
+      <c r="I4" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="29">
+        <v>-4.06092498451471E-4</v>
+      </c>
+      <c r="B5" s="29">
+        <v>-0.15244589745998399</v>
+      </c>
+      <c r="C5" s="29">
+        <v>-1.21209200005978E-3</v>
+      </c>
+      <c r="D5" s="29">
+        <v>-0.117412149906158</v>
+      </c>
+      <c r="E5" s="29">
+        <v>-2.6462823152542101E-3</v>
+      </c>
+      <c r="F5" s="29">
+        <v>0.85134243965148904</v>
+      </c>
+      <c r="G5" s="29">
+        <v>0</v>
+      </c>
+      <c r="H5" s="29">
+        <v>0</v>
+      </c>
+      <c r="I5" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="29">
+        <v>5.05214463919401E-3</v>
+      </c>
+      <c r="B6" s="29">
+        <v>-0.157537400722504</v>
+      </c>
+      <c r="C6" s="29">
+        <v>-6.2086973339319203E-3</v>
+      </c>
+      <c r="D6" s="29">
+        <v>-0.29486876726150502</v>
+      </c>
+      <c r="E6" s="29">
+        <v>-2.80796959996223E-2</v>
+      </c>
+      <c r="F6" s="29">
+        <v>0.56537818908691395</v>
+      </c>
+      <c r="G6" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H6" s="29">
+        <v>0</v>
+      </c>
+      <c r="I6" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="29">
+        <v>3.71134956367314E-5</v>
+      </c>
+      <c r="B7" s="29">
+        <v>-0.19372102618217499</v>
+      </c>
+      <c r="C7" s="29">
+        <v>-2.1289892029017201E-3</v>
+      </c>
+      <c r="D7" s="29">
+        <v>-0.41201990842819203</v>
+      </c>
+      <c r="E7" s="29">
+        <v>-1.1864490807056401E-3</v>
+      </c>
+      <c r="F7" s="29">
+        <v>0.55889892578125</v>
+      </c>
+      <c r="G7" s="29">
+        <v>0</v>
+      </c>
+      <c r="H7" s="29">
+        <v>0</v>
+      </c>
+      <c r="I7" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="29">
+        <v>-8.9350854977965398E-4</v>
+      </c>
+      <c r="B8" s="29">
+        <v>4.2732272297143901E-2</v>
+      </c>
+      <c r="C8" s="29">
+        <v>-7.74873793125153E-2</v>
+      </c>
+      <c r="D8" s="29">
+        <v>0.62493914365768399</v>
+      </c>
+      <c r="E8" s="29">
+        <v>-0.52349442243576105</v>
+      </c>
+      <c r="F8" s="29">
+        <v>-0.28826642036437999</v>
+      </c>
+      <c r="G8" s="29">
+        <v>0</v>
+      </c>
+      <c r="H8" s="29">
+        <v>0</v>
+      </c>
+      <c r="I8" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="29">
+        <v>-8.9688366279006004E-4</v>
+      </c>
+      <c r="B9" s="29">
+        <v>4.1764143854379703E-2</v>
+      </c>
+      <c r="C9" s="29">
+        <v>-7.7566295862197904E-2</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0.45929118990898099</v>
+      </c>
+      <c r="E9" s="29">
+        <v>-0.41274711489677401</v>
+      </c>
+      <c r="F9" s="29">
+        <v>-0.223745286464691</v>
+      </c>
+      <c r="G9" s="29">
+        <v>0</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0</v>
+      </c>
+      <c r="I9" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="29">
+        <v>-5.51847275346518E-4</v>
+      </c>
+      <c r="B10" s="29">
+        <v>6.6554106771945995E-2</v>
+      </c>
+      <c r="C10" s="29">
+        <v>-0.119616024196148</v>
+      </c>
+      <c r="D10" s="29">
+        <v>0.49095398187637301</v>
+      </c>
+      <c r="E10" s="29">
+        <v>-0.47584062814712502</v>
+      </c>
+      <c r="F10" s="29">
+        <v>-0.25870200991630599</v>
+      </c>
+      <c r="G10" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H10" s="29">
+        <v>0</v>
+      </c>
+      <c r="I10" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="29">
+        <v>-3.2309396192431499E-4</v>
+      </c>
+      <c r="B11" s="29">
+        <v>3.5572569817304597E-2</v>
+      </c>
+      <c r="C11" s="29">
+        <v>-6.1782382428646102E-2</v>
+      </c>
+      <c r="D11" s="29">
+        <v>0.27096122503280601</v>
+      </c>
+      <c r="E11" s="29">
+        <v>-0.21531303226947801</v>
+      </c>
+      <c r="F11" s="29">
+        <v>-0.122712507843971</v>
+      </c>
+      <c r="G11" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H11" s="29">
+        <v>0</v>
+      </c>
+      <c r="I11" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="29">
+        <v>-7.1692815981805303E-4</v>
+      </c>
+      <c r="B12" s="29">
+        <v>3.56008112430573E-2</v>
+      </c>
+      <c r="C12" s="29">
+        <v>-6.2020469456911101E-2</v>
+      </c>
+      <c r="D12" s="29">
+        <v>-6.5964758396148699E-3</v>
+      </c>
+      <c r="E12" s="29">
+        <v>-0.30639430880546598</v>
+      </c>
+      <c r="F12" s="29">
+        <v>-0.17468151450157199</v>
+      </c>
+      <c r="G12" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H12" s="29">
+        <v>0</v>
+      </c>
+      <c r="I12" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="29">
+        <v>-1.24058220535517E-3</v>
+      </c>
+      <c r="B13" s="29">
+        <v>6.9012217223644298E-2</v>
+      </c>
+      <c r="C13" s="29">
+        <v>-0.119697146117687</v>
+      </c>
+      <c r="D13" s="29">
+        <v>-5.5351331830024698E-2</v>
+      </c>
+      <c r="E13" s="29">
+        <v>-0.59383064508438099</v>
+      </c>
+      <c r="F13" s="29">
+        <v>-0.33820247650146501</v>
+      </c>
+      <c r="G13" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H13" s="29">
+        <v>0</v>
+      </c>
+      <c r="I13" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="29">
+        <v>-7.1821291930973497E-4</v>
+      </c>
+      <c r="B14" s="29">
+        <v>4.6037148684263202E-2</v>
+      </c>
+      <c r="C14" s="29">
+        <v>-7.8464329242706299E-2</v>
+      </c>
+      <c r="D14" s="29">
+        <v>-7.8753150999546107E-2</v>
+      </c>
+      <c r="E14" s="29">
+        <v>-0.286407381296158</v>
+      </c>
+      <c r="F14" s="29">
+        <v>-0.16520524024963401</v>
+      </c>
+      <c r="G14" s="29">
+        <v>0</v>
+      </c>
+      <c r="H14" s="29">
+        <v>0</v>
+      </c>
+      <c r="I14" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="29">
+        <v>-6.2177400104701497E-4</v>
+      </c>
+      <c r="B15" s="29">
+        <v>3.2626789063215297E-2</v>
+      </c>
+      <c r="C15" s="29">
+        <v>-5.72014674544334E-2</v>
+      </c>
+      <c r="D15" s="29">
+        <v>-2.7179472148418399E-2</v>
+      </c>
+      <c r="E15" s="29">
+        <v>-0.194883912801743</v>
+      </c>
+      <c r="F15" s="29">
+        <v>-0.10984055697917899</v>
+      </c>
+      <c r="G15" s="29">
+        <v>0</v>
+      </c>
+      <c r="H15" s="29">
+        <v>0</v>
+      </c>
+      <c r="I15" s="29">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
@@ -4937,7 +6997,7 @@
       <c r="L1" s="27"/>
       <c r="M1" s="28"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -4975,7 +7035,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.198836579918861</v>
       </c>
@@ -5019,7 +7079,7 @@
         <v>0.198836579918861</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.25498384237289401</v>
       </c>
@@ -5063,7 +7123,7 @@
         <v>0.25498384237289401</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.50102174282073997</v>
       </c>
@@ -5107,7 +7167,7 @@
         <v>0.50102174282073997</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.38675421476364102</v>
       </c>
@@ -5151,7 +7211,7 @@
         <v>0.38675421476364102</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.85134243965148904</v>
       </c>
@@ -5195,7 +7255,7 @@
         <v>0.85134243965148904</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.56537818908691395</v>
       </c>
@@ -5239,7 +7299,7 @@
         <v>0.56537818908691395</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.55889892578125</v>
       </c>
@@ -5283,7 +7343,7 @@
         <v>0.55889892578125</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-0.28826642036437999</v>
       </c>
@@ -5327,7 +7387,7 @@
         <v>-0.28826642036437999</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-0.223745286464691</v>
       </c>
@@ -5371,7 +7431,7 @@
         <v>-0.223745286464691</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-0.25870200991630599</v>
       </c>
@@ -5415,7 +7475,7 @@
         <v>-0.25870200991630599</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-0.122712507843971</v>
       </c>
@@ -5459,7 +7519,7 @@
         <v>-0.122712507843971</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-0.17468151450157199</v>
       </c>
@@ -5503,7 +7563,7 @@
         <v>-0.17468151450157199</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-0.33820247650146501</v>
       </c>
@@ -5547,7 +7607,7 @@
         <v>-0.33820247650146501</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-0.16520524024963401</v>
       </c>
@@ -5591,7 +7651,7 @@
         <v>-0.16520524024963401</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>-0.10984055697917899</v>
       </c>
@@ -5635,7 +7695,7 @@
         <v>-0.10984055697917899</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H18">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5661,7 +7721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5687,7 +7747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5713,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5739,7 +7799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H22">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5765,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5791,7 +7851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5817,7 +7877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5843,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5869,7 +7929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H27">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5895,7 +7955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H28">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5931,6 +7991,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -6183,7 +8251,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6192,15 +8260,24 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6219,27 +8296,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>